--- a/artfynd/A 28951-2024 artfynd.xlsx
+++ b/artfynd/A 28951-2024 artfynd.xlsx
@@ -1306,10 +1306,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118793587</v>
+        <v>118793377</v>
       </c>
       <c r="B8" t="n">
-        <v>79469</v>
+        <v>78484</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1318,25 +1318,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1346,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>879116</v>
+        <v>879103</v>
       </c>
       <c r="R8" t="n">
-        <v>7410673</v>
+        <v>7410568</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1408,10 +1408,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118793588</v>
+        <v>118793359</v>
       </c>
       <c r="B9" t="n">
-        <v>79469</v>
+        <v>90558</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1420,25 +1420,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6456</v>
+        <v>3277</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(O.F.Müll.:Fr.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1448,10 +1448,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>879064</v>
+        <v>879308</v>
       </c>
       <c r="R9" t="n">
-        <v>7410567</v>
+        <v>7410737</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1510,10 +1510,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118793377</v>
+        <v>118793360</v>
       </c>
       <c r="B10" t="n">
-        <v>78484</v>
+        <v>90522</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1526,21 +1526,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1550,10 +1550,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>879103</v>
+        <v>879042</v>
       </c>
       <c r="R10" t="n">
-        <v>7410568</v>
+        <v>7410510</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1586,6 +1586,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1612,10 +1617,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118793359</v>
+        <v>118793587</v>
       </c>
       <c r="B11" t="n">
-        <v>90558</v>
+        <v>79469</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1624,25 +1629,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3277</v>
+        <v>6456</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(O.F.Müll.:Fr.) Dentinger &amp; D.J.McLaughlin</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1652,10 +1657,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>879308</v>
+        <v>879116</v>
       </c>
       <c r="R11" t="n">
-        <v>7410737</v>
+        <v>7410673</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1714,10 +1719,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118793360</v>
+        <v>118793588</v>
       </c>
       <c r="B12" t="n">
-        <v>90522</v>
+        <v>79469</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1726,25 +1731,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1754,10 +1759,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>879042</v>
+        <v>879064</v>
       </c>
       <c r="R12" t="n">
-        <v>7410510</v>
+        <v>7410567</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1790,11 +1795,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 28951-2024 artfynd.xlsx
+++ b/artfynd/A 28951-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118793577</v>
+        <v>118793359</v>
       </c>
       <c r="B2" t="n">
-        <v>57290</v>
+        <v>90558</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>3277</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(O.F.Müll.:Fr.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>879114</v>
+        <v>879308</v>
       </c>
       <c r="R2" t="n">
-        <v>7410564</v>
+        <v>7410737</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Bohål</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118793578</v>
+        <v>118793366</v>
       </c>
       <c r="B3" t="n">
-        <v>57290</v>
+        <v>78484</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>879261</v>
+        <v>879121</v>
       </c>
       <c r="R3" t="n">
-        <v>7410686</v>
+        <v>7410856</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -858,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Avbarkat</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118794496</v>
+        <v>118793365</v>
       </c>
       <c r="B4" t="n">
-        <v>57290</v>
+        <v>78484</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,38 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Turkinrova, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>879055</v>
+        <v>879126</v>
       </c>
       <c r="R4" t="n">
-        <v>7410850</v>
+        <v>7410862</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -969,11 +955,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118793372</v>
+        <v>118793360</v>
       </c>
       <c r="B5" t="n">
-        <v>78484</v>
+        <v>90522</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1016,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1040,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>879147</v>
+        <v>879042</v>
       </c>
       <c r="R5" t="n">
-        <v>7410683</v>
+        <v>7410510</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1076,6 +1057,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1102,7 +1088,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118793364</v>
+        <v>118793368</v>
       </c>
       <c r="B6" t="n">
         <v>78484</v>
@@ -1142,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>879242</v>
+        <v>879068</v>
       </c>
       <c r="R6" t="n">
-        <v>7410815</v>
+        <v>7410854</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1204,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118793584</v>
+        <v>118793579</v>
       </c>
       <c r="B7" t="n">
-        <v>57306</v>
+        <v>57290</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1220,16 +1206,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1244,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>879242</v>
+        <v>879307</v>
       </c>
       <c r="R7" t="n">
-        <v>7410814</v>
+        <v>7410761</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1282,6 +1268,11 @@
           <t>2024-07-29</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Avbarkat</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1299,14 +1290,14 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson, Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118793377</v>
+        <v>118793363</v>
       </c>
       <c r="B8" t="n">
         <v>78484</v>
@@ -1346,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>879103</v>
+        <v>879291</v>
       </c>
       <c r="R8" t="n">
-        <v>7410568</v>
+        <v>7410669</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1408,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118793359</v>
+        <v>118793588</v>
       </c>
       <c r="B9" t="n">
-        <v>90558</v>
+        <v>79469</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1420,25 +1411,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3277</v>
+        <v>6456</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(O.F.Müll.:Fr.) Dentinger &amp; D.J.McLaughlin</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1448,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>879308</v>
+        <v>879064</v>
       </c>
       <c r="R9" t="n">
-        <v>7410737</v>
+        <v>7410567</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1510,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118793360</v>
+        <v>118793577</v>
       </c>
       <c r="B10" t="n">
-        <v>90522</v>
+        <v>57290</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1526,21 +1517,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1550,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>879042</v>
+        <v>879114</v>
       </c>
       <c r="R10" t="n">
-        <v>7410510</v>
+        <v>7410564</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1590,7 +1581,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2 stycken</t>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1610,17 +1601,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson, Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118793587</v>
+        <v>118793372</v>
       </c>
       <c r="B11" t="n">
-        <v>79469</v>
+        <v>78484</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1629,25 +1620,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1657,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>879116</v>
+        <v>879147</v>
       </c>
       <c r="R11" t="n">
-        <v>7410673</v>
+        <v>7410683</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1719,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118793588</v>
+        <v>118793362</v>
       </c>
       <c r="B12" t="n">
-        <v>79469</v>
+        <v>78484</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1731,25 +1722,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1759,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>879064</v>
+        <v>879153</v>
       </c>
       <c r="R12" t="n">
-        <v>7410567</v>
+        <v>7410579</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1821,7 +1812,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118793362</v>
+        <v>118793370</v>
       </c>
       <c r="B13" t="n">
         <v>78484</v>
@@ -1861,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>879153</v>
+        <v>879185</v>
       </c>
       <c r="R13" t="n">
-        <v>7410579</v>
+        <v>7410814</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1923,10 +1914,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118793373</v>
+        <v>118793587</v>
       </c>
       <c r="B14" t="n">
-        <v>78484</v>
+        <v>79469</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1935,25 +1926,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2025,7 +2016,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118793579</v>
+        <v>118793578</v>
       </c>
       <c r="B15" t="n">
         <v>57290</v>
@@ -2065,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>879307</v>
+        <v>879261</v>
       </c>
       <c r="R15" t="n">
-        <v>7410761</v>
+        <v>7410686</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2125,14 +2116,14 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson, Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118793368</v>
+        <v>118793367</v>
       </c>
       <c r="B16" t="n">
         <v>78484</v>
@@ -2172,10 +2163,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>879068</v>
+        <v>879104</v>
       </c>
       <c r="R16" t="n">
-        <v>7410854</v>
+        <v>7410851</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2234,7 +2225,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118793366</v>
+        <v>118793374</v>
       </c>
       <c r="B17" t="n">
         <v>78484</v>
@@ -2274,10 +2265,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>879121</v>
+        <v>879113</v>
       </c>
       <c r="R17" t="n">
-        <v>7410856</v>
+        <v>7410609</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2336,10 +2327,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118793580</v>
+        <v>118793377</v>
       </c>
       <c r="B18" t="n">
-        <v>57290</v>
+        <v>78484</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2352,21 +2343,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2376,10 +2367,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>879242</v>
+        <v>879103</v>
       </c>
       <c r="R18" t="n">
-        <v>7410815</v>
+        <v>7410568</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2412,11 +2403,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Avbarkat</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2443,10 +2429,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118793586</v>
+        <v>118793589</v>
       </c>
       <c r="B19" t="n">
-        <v>57306</v>
+        <v>79469</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2455,25 +2441,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2483,10 +2469,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>879119</v>
+        <v>879066</v>
       </c>
       <c r="R19" t="n">
-        <v>7410609</v>
+        <v>7410571</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2545,7 +2531,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118793363</v>
+        <v>118793371</v>
       </c>
       <c r="B20" t="n">
         <v>78484</v>
@@ -2585,10 +2571,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>879291</v>
+        <v>879153</v>
       </c>
       <c r="R20" t="n">
-        <v>7410669</v>
+        <v>7410722</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2647,10 +2633,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118793365</v>
+        <v>118793584</v>
       </c>
       <c r="B21" t="n">
-        <v>78484</v>
+        <v>57306</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2663,21 +2649,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2687,10 +2673,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>879126</v>
+        <v>879242</v>
       </c>
       <c r="R21" t="n">
-        <v>7410862</v>
+        <v>7410814</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2749,10 +2735,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118793367</v>
+        <v>118794496</v>
       </c>
       <c r="B22" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2765,34 +2751,38 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Turkinrova, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>879104</v>
+        <v>879055</v>
       </c>
       <c r="R22" t="n">
-        <v>7410851</v>
+        <v>7410850</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2825,6 +2815,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2851,10 +2846,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118793370</v>
+        <v>118793586</v>
       </c>
       <c r="B23" t="n">
-        <v>78484</v>
+        <v>57306</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2867,21 +2862,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2891,10 +2886,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>879185</v>
+        <v>879119</v>
       </c>
       <c r="R23" t="n">
-        <v>7410814</v>
+        <v>7410609</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2953,10 +2948,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118793589</v>
+        <v>118793585</v>
       </c>
       <c r="B24" t="n">
-        <v>79469</v>
+        <v>57306</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2965,25 +2960,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2993,10 +2988,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>879066</v>
+        <v>879078</v>
       </c>
       <c r="R24" t="n">
-        <v>7410571</v>
+        <v>7410852</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3055,10 +3050,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118793585</v>
+        <v>118793373</v>
       </c>
       <c r="B25" t="n">
-        <v>57306</v>
+        <v>78484</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3071,21 +3066,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3095,10 +3090,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>879078</v>
+        <v>879116</v>
       </c>
       <c r="R25" t="n">
-        <v>7410852</v>
+        <v>7410673</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3157,7 +3152,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118793374</v>
+        <v>118793364</v>
       </c>
       <c r="B26" t="n">
         <v>78484</v>
@@ -3197,10 +3192,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>879113</v>
+        <v>879242</v>
       </c>
       <c r="R26" t="n">
-        <v>7410609</v>
+        <v>7410815</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3259,10 +3254,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118793371</v>
+        <v>118793580</v>
       </c>
       <c r="B27" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3275,21 +3270,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3299,10 +3294,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>879153</v>
+        <v>879242</v>
       </c>
       <c r="R27" t="n">
-        <v>7410722</v>
+        <v>7410815</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3337,6 +3332,11 @@
           <t>2024-07-29</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Avbarkat</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3354,7 +3354,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson, Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>

--- a/artfynd/A 28951-2024 artfynd.xlsx
+++ b/artfynd/A 28951-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118793359</v>
+        <v>118793377</v>
       </c>
       <c r="B2" t="n">
-        <v>90558</v>
+        <v>78484</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3277</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(O.F.Müll.:Fr.) Dentinger &amp; D.J.McLaughlin</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>879308</v>
+        <v>879103</v>
       </c>
       <c r="R2" t="n">
-        <v>7410737</v>
+        <v>7410568</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118793366</v>
+        <v>118793578</v>
       </c>
       <c r="B3" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>879121</v>
+        <v>879261</v>
       </c>
       <c r="R3" t="n">
-        <v>7410856</v>
+        <v>7410686</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -855,6 +855,11 @@
           <t>2024-07-29</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Avbarkat</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -872,7 +877,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson, Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -981,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118793360</v>
+        <v>118793371</v>
       </c>
       <c r="B5" t="n">
-        <v>90522</v>
+        <v>78484</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>879042</v>
+        <v>879153</v>
       </c>
       <c r="R5" t="n">
-        <v>7410510</v>
+        <v>7410722</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1057,11 +1062,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118793368</v>
+        <v>118793586</v>
       </c>
       <c r="B6" t="n">
-        <v>78484</v>
+        <v>57306</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>879068</v>
+        <v>879119</v>
       </c>
       <c r="R6" t="n">
-        <v>7410854</v>
+        <v>7410609</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1183,17 +1183,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson, Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118793579</v>
+        <v>118793588</v>
       </c>
       <c r="B7" t="n">
-        <v>57290</v>
+        <v>79469</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,25 +1202,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>879307</v>
+        <v>879064</v>
       </c>
       <c r="R7" t="n">
-        <v>7410761</v>
+        <v>7410567</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1266,11 +1266,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Avbarkat</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,7 +1292,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118793363</v>
+        <v>118793364</v>
       </c>
       <c r="B8" t="n">
         <v>78484</v>
@@ -1337,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>879291</v>
+        <v>879242</v>
       </c>
       <c r="R8" t="n">
-        <v>7410669</v>
+        <v>7410815</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1399,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118793588</v>
+        <v>118793359</v>
       </c>
       <c r="B9" t="n">
-        <v>79469</v>
+        <v>90558</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1411,25 +1406,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6456</v>
+        <v>3277</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(O.F.Müll.:Fr.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>879064</v>
+        <v>879308</v>
       </c>
       <c r="R9" t="n">
-        <v>7410567</v>
+        <v>7410737</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1501,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118793577</v>
+        <v>118793362</v>
       </c>
       <c r="B10" t="n">
-        <v>57290</v>
+        <v>78484</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>879114</v>
+        <v>879153</v>
       </c>
       <c r="R10" t="n">
-        <v>7410564</v>
+        <v>7410579</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1579,11 +1574,6 @@
           <t>2024-07-29</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Bohål</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1601,14 +1591,14 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Marie Persson, Viktoria Sturk</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118793372</v>
+        <v>118793366</v>
       </c>
       <c r="B11" t="n">
         <v>78484</v>
@@ -1648,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>879147</v>
+        <v>879121</v>
       </c>
       <c r="R11" t="n">
-        <v>7410683</v>
+        <v>7410856</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1710,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118793362</v>
+        <v>118793360</v>
       </c>
       <c r="B12" t="n">
-        <v>78484</v>
+        <v>90522</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1726,21 +1716,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1750,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>879153</v>
+        <v>879042</v>
       </c>
       <c r="R12" t="n">
-        <v>7410579</v>
+        <v>7410510</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1786,6 +1776,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1812,7 +1807,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118793370</v>
+        <v>118793363</v>
       </c>
       <c r="B13" t="n">
         <v>78484</v>
@@ -1852,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>879185</v>
+        <v>879291</v>
       </c>
       <c r="R13" t="n">
-        <v>7410814</v>
+        <v>7410669</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1914,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118793587</v>
+        <v>118793367</v>
       </c>
       <c r="B14" t="n">
-        <v>79469</v>
+        <v>78484</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1926,25 +1921,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1954,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>879116</v>
+        <v>879104</v>
       </c>
       <c r="R14" t="n">
-        <v>7410673</v>
+        <v>7410851</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2016,10 +2011,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118793578</v>
+        <v>118793585</v>
       </c>
       <c r="B15" t="n">
-        <v>57290</v>
+        <v>57306</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2032,16 +2027,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2056,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>879261</v>
+        <v>879078</v>
       </c>
       <c r="R15" t="n">
-        <v>7410686</v>
+        <v>7410852</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2092,11 +2087,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Avbarkat</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2123,7 +2113,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118793367</v>
+        <v>118793373</v>
       </c>
       <c r="B16" t="n">
         <v>78484</v>
@@ -2163,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>879104</v>
+        <v>879116</v>
       </c>
       <c r="R16" t="n">
-        <v>7410851</v>
+        <v>7410673</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2225,7 +2215,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118793374</v>
+        <v>118793368</v>
       </c>
       <c r="B17" t="n">
         <v>78484</v>
@@ -2265,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>879113</v>
+        <v>879068</v>
       </c>
       <c r="R17" t="n">
-        <v>7410609</v>
+        <v>7410854</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2327,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118793377</v>
+        <v>118793587</v>
       </c>
       <c r="B18" t="n">
-        <v>78484</v>
+        <v>79469</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2339,25 +2329,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2367,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>879103</v>
+        <v>879116</v>
       </c>
       <c r="R18" t="n">
-        <v>7410568</v>
+        <v>7410673</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2422,17 +2412,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson, Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118793589</v>
+        <v>118793374</v>
       </c>
       <c r="B19" t="n">
-        <v>79469</v>
+        <v>78484</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2441,25 +2431,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2469,10 +2459,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>879066</v>
+        <v>879113</v>
       </c>
       <c r="R19" t="n">
-        <v>7410571</v>
+        <v>7410609</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2531,10 +2521,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118793371</v>
+        <v>118793577</v>
       </c>
       <c r="B20" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2547,21 +2537,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2571,10 +2561,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>879153</v>
+        <v>879114</v>
       </c>
       <c r="R20" t="n">
-        <v>7410722</v>
+        <v>7410564</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2609,6 +2599,11 @@
           <t>2024-07-29</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Bohål</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2626,17 +2621,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson, Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118793584</v>
+        <v>118793372</v>
       </c>
       <c r="B21" t="n">
-        <v>57306</v>
+        <v>78484</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2649,21 +2644,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2673,10 +2668,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>879242</v>
+        <v>879147</v>
       </c>
       <c r="R21" t="n">
-        <v>7410814</v>
+        <v>7410683</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2735,10 +2730,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118794496</v>
+        <v>118793589</v>
       </c>
       <c r="B22" t="n">
-        <v>57290</v>
+        <v>79469</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2747,42 +2742,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Turkinrova, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>879055</v>
+        <v>879066</v>
       </c>
       <c r="R22" t="n">
-        <v>7410850</v>
+        <v>7410571</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2817,11 +2808,6 @@
           <t>2024-07-29</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -2839,17 +2825,17 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson, Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118793586</v>
+        <v>118793370</v>
       </c>
       <c r="B23" t="n">
-        <v>57306</v>
+        <v>78484</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2862,21 +2848,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2886,10 +2872,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>879119</v>
+        <v>879185</v>
       </c>
       <c r="R23" t="n">
-        <v>7410609</v>
+        <v>7410814</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2948,10 +2934,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118793585</v>
+        <v>118793579</v>
       </c>
       <c r="B24" t="n">
-        <v>57306</v>
+        <v>57290</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2964,16 +2950,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2988,10 +2974,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>879078</v>
+        <v>879307</v>
       </c>
       <c r="R24" t="n">
-        <v>7410852</v>
+        <v>7410761</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3026,6 +3012,11 @@
           <t>2024-07-29</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Avbarkat</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3043,17 +3034,17 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson, Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118793373</v>
+        <v>118793580</v>
       </c>
       <c r="B25" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3066,21 +3057,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3090,10 +3081,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>879116</v>
+        <v>879242</v>
       </c>
       <c r="R25" t="n">
-        <v>7410673</v>
+        <v>7410815</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3128,6 +3119,11 @@
           <t>2024-07-29</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Avbarkat</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3145,17 +3141,17 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson, Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118793364</v>
+        <v>118794496</v>
       </c>
       <c r="B26" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3168,34 +3164,38 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Turkinrova, Nb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>879242</v>
+        <v>879055</v>
       </c>
       <c r="R26" t="n">
-        <v>7410815</v>
+        <v>7410850</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3228,6 +3228,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3254,10 +3259,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118793580</v>
+        <v>118793584</v>
       </c>
       <c r="B27" t="n">
-        <v>57290</v>
+        <v>57306</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3270,16 +3275,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3297,7 +3302,7 @@
         <v>879242</v>
       </c>
       <c r="R27" t="n">
-        <v>7410815</v>
+        <v>7410814</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3330,11 +3335,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Avbarkat</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 28951-2024 artfynd.xlsx
+++ b/artfynd/A 28951-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118793377</v>
+        <v>118793367</v>
       </c>
       <c r="B2" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>879103</v>
+        <v>879104</v>
       </c>
       <c r="R2" t="n">
-        <v>7410568</v>
+        <v>7410851</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118793578</v>
+        <v>118793362</v>
       </c>
       <c r="B3" t="n">
-        <v>57290</v>
+        <v>78491</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>879261</v>
+        <v>879153</v>
       </c>
       <c r="R3" t="n">
-        <v>7410686</v>
+        <v>7410579</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -855,11 +855,6 @@
           <t>2024-07-29</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Avbarkat</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -877,17 +872,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Marie Persson, Viktoria Sturk</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118793365</v>
+        <v>118793360</v>
       </c>
       <c r="B4" t="n">
-        <v>78484</v>
+        <v>90529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>879126</v>
+        <v>879042</v>
       </c>
       <c r="R4" t="n">
-        <v>7410862</v>
+        <v>7410510</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -960,6 +955,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118793371</v>
+        <v>118794496</v>
       </c>
       <c r="B5" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,34 +1002,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Turkinrova, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>879153</v>
+        <v>879055</v>
       </c>
       <c r="R5" t="n">
-        <v>7410722</v>
+        <v>7410850</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1062,6 +1066,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,10 +1097,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118793586</v>
+        <v>118793366</v>
       </c>
       <c r="B6" t="n">
-        <v>57306</v>
+        <v>78491</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1113,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>879119</v>
+        <v>879121</v>
       </c>
       <c r="R6" t="n">
-        <v>7410609</v>
+        <v>7410856</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1183,17 +1192,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Marie Persson, Viktoria Sturk</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118793588</v>
+        <v>118793579</v>
       </c>
       <c r="B7" t="n">
-        <v>79469</v>
+        <v>57290</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,25 +1211,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1239,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>879064</v>
+        <v>879307</v>
       </c>
       <c r="R7" t="n">
-        <v>7410567</v>
+        <v>7410761</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1268,6 +1277,11 @@
           <t>2024-07-29</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Avbarkat</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1285,17 +1299,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Marie Persson, Viktoria Sturk</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118793364</v>
+        <v>118793377</v>
       </c>
       <c r="B8" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1332,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>879242</v>
+        <v>879103</v>
       </c>
       <c r="R8" t="n">
-        <v>7410815</v>
+        <v>7410568</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1394,10 +1408,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118793359</v>
+        <v>118793372</v>
       </c>
       <c r="B9" t="n">
-        <v>90558</v>
+        <v>78491</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,21 +1424,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3277</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(O.F.Müll.:Fr.) Dentinger &amp; D.J.McLaughlin</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1448,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>879308</v>
+        <v>879147</v>
       </c>
       <c r="R9" t="n">
-        <v>7410737</v>
+        <v>7410683</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1496,10 +1510,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118793362</v>
+        <v>118793365</v>
       </c>
       <c r="B10" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1536,10 +1550,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>879153</v>
+        <v>879126</v>
       </c>
       <c r="R10" t="n">
-        <v>7410579</v>
+        <v>7410862</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1598,10 +1612,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118793366</v>
+        <v>118793370</v>
       </c>
       <c r="B11" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1638,10 +1652,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>879121</v>
+        <v>879185</v>
       </c>
       <c r="R11" t="n">
-        <v>7410856</v>
+        <v>7410814</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1700,10 +1714,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118793360</v>
+        <v>118793587</v>
       </c>
       <c r="B12" t="n">
-        <v>90522</v>
+        <v>79476</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1712,25 +1726,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1754,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>879042</v>
+        <v>879116</v>
       </c>
       <c r="R12" t="n">
-        <v>7410510</v>
+        <v>7410673</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1776,11 +1790,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1807,10 +1816,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118793363</v>
+        <v>118793580</v>
       </c>
       <c r="B13" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1823,21 +1832,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1847,10 +1856,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>879291</v>
+        <v>879242</v>
       </c>
       <c r="R13" t="n">
-        <v>7410669</v>
+        <v>7410815</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1883,6 +1892,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Avbarkat</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1909,10 +1923,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118793367</v>
+        <v>118793585</v>
       </c>
       <c r="B14" t="n">
-        <v>78484</v>
+        <v>57306</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1925,21 +1939,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1949,10 +1963,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>879104</v>
+        <v>879078</v>
       </c>
       <c r="R14" t="n">
-        <v>7410851</v>
+        <v>7410852</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2011,10 +2025,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118793585</v>
+        <v>118793363</v>
       </c>
       <c r="B15" t="n">
-        <v>57306</v>
+        <v>78491</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2027,21 +2041,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2051,10 +2065,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>879078</v>
+        <v>879291</v>
       </c>
       <c r="R15" t="n">
-        <v>7410852</v>
+        <v>7410669</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2106,17 +2120,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Marie Persson, Viktoria Sturk</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118793373</v>
+        <v>118793584</v>
       </c>
       <c r="B16" t="n">
-        <v>78484</v>
+        <v>57306</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2129,21 +2143,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2167,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>879116</v>
+        <v>879242</v>
       </c>
       <c r="R16" t="n">
-        <v>7410673</v>
+        <v>7410814</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2215,10 +2229,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118793368</v>
+        <v>118793577</v>
       </c>
       <c r="B17" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2231,21 +2245,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2255,10 +2269,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>879068</v>
+        <v>879114</v>
       </c>
       <c r="R17" t="n">
-        <v>7410854</v>
+        <v>7410564</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2291,6 +2305,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2317,10 +2336,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118793587</v>
+        <v>118793586</v>
       </c>
       <c r="B18" t="n">
-        <v>79469</v>
+        <v>57306</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2329,25 +2348,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2357,10 +2376,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>879116</v>
+        <v>879119</v>
       </c>
       <c r="R18" t="n">
-        <v>7410673</v>
+        <v>7410609</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2412,17 +2431,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Marie Persson, Viktoria Sturk</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118793374</v>
+        <v>118793359</v>
       </c>
       <c r="B19" t="n">
-        <v>78484</v>
+        <v>90565</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2435,21 +2454,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>3277</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(O.F.Müll.:Fr.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2459,10 +2478,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>879113</v>
+        <v>879308</v>
       </c>
       <c r="R19" t="n">
-        <v>7410609</v>
+        <v>7410737</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2521,10 +2540,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118793577</v>
+        <v>118793373</v>
       </c>
       <c r="B20" t="n">
-        <v>57290</v>
+        <v>78491</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2537,21 +2556,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2561,10 +2580,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>879114</v>
+        <v>879116</v>
       </c>
       <c r="R20" t="n">
-        <v>7410564</v>
+        <v>7410673</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2599,11 +2618,6 @@
           <t>2024-07-29</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Bohål</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2621,17 +2635,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Marie Persson, Viktoria Sturk</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118793372</v>
+        <v>118793589</v>
       </c>
       <c r="B21" t="n">
-        <v>78484</v>
+        <v>79476</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2640,25 +2654,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2668,10 +2682,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>879147</v>
+        <v>879066</v>
       </c>
       <c r="R21" t="n">
-        <v>7410683</v>
+        <v>7410571</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2730,10 +2744,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118793589</v>
+        <v>118793374</v>
       </c>
       <c r="B22" t="n">
-        <v>79469</v>
+        <v>78491</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2742,25 +2756,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2770,10 +2784,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>879066</v>
+        <v>879113</v>
       </c>
       <c r="R22" t="n">
-        <v>7410571</v>
+        <v>7410609</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2825,17 +2839,17 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Marie Persson, Viktoria Sturk</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118793370</v>
+        <v>118793368</v>
       </c>
       <c r="B23" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2872,10 +2886,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>879185</v>
+        <v>879068</v>
       </c>
       <c r="R23" t="n">
-        <v>7410814</v>
+        <v>7410854</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2934,10 +2948,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118793579</v>
+        <v>118793371</v>
       </c>
       <c r="B24" t="n">
-        <v>57290</v>
+        <v>78491</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2950,21 +2964,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2974,10 +2988,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>879307</v>
+        <v>879153</v>
       </c>
       <c r="R24" t="n">
-        <v>7410761</v>
+        <v>7410722</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3012,11 +3026,6 @@
           <t>2024-07-29</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Avbarkat</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3034,17 +3043,17 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Marie Persson, Viktoria Sturk</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118793580</v>
+        <v>118793588</v>
       </c>
       <c r="B25" t="n">
-        <v>57290</v>
+        <v>79476</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3053,25 +3062,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3081,10 +3090,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>879242</v>
+        <v>879064</v>
       </c>
       <c r="R25" t="n">
-        <v>7410815</v>
+        <v>7410567</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3119,11 +3128,6 @@
           <t>2024-07-29</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Avbarkat</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3141,17 +3145,17 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Marie Persson, Viktoria Sturk</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118794496</v>
+        <v>118793364</v>
       </c>
       <c r="B26" t="n">
-        <v>57290</v>
+        <v>78491</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3164,38 +3168,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Turkinrova, Nb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>879055</v>
+        <v>879242</v>
       </c>
       <c r="R26" t="n">
-        <v>7410850</v>
+        <v>7410815</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3228,11 +3228,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3259,10 +3254,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118793584</v>
+        <v>118793578</v>
       </c>
       <c r="B27" t="n">
-        <v>57306</v>
+        <v>57290</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3275,16 +3270,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3299,10 +3294,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>879242</v>
+        <v>879261</v>
       </c>
       <c r="R27" t="n">
-        <v>7410814</v>
+        <v>7410686</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3337,6 +3332,11 @@
           <t>2024-07-29</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Avbarkat</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3354,7 +3354,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Marie Persson, Viktoria Sturk</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>

--- a/artfynd/A 28951-2024 artfynd.xlsx
+++ b/artfynd/A 28951-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118793367</v>
+        <v>118793363</v>
       </c>
       <c r="B2" t="n">
         <v>78491</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>879104</v>
+        <v>879291</v>
       </c>
       <c r="R2" t="n">
-        <v>7410851</v>
+        <v>7410669</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118793362</v>
+        <v>118793585</v>
       </c>
       <c r="B3" t="n">
-        <v>78491</v>
+        <v>57306</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>879153</v>
+        <v>879078</v>
       </c>
       <c r="R3" t="n">
-        <v>7410579</v>
+        <v>7410852</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118793360</v>
+        <v>118793578</v>
       </c>
       <c r="B4" t="n">
-        <v>90529</v>
+        <v>57290</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>879042</v>
+        <v>879261</v>
       </c>
       <c r="R4" t="n">
-        <v>7410510</v>
+        <v>7410686</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2 stycken</t>
+          <t>Avbarkat</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118794496</v>
+        <v>118793374</v>
       </c>
       <c r="B5" t="n">
-        <v>57290</v>
+        <v>78491</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,38 +1002,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Turkinrova, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>879055</v>
+        <v>879113</v>
       </c>
       <c r="R5" t="n">
-        <v>7410850</v>
+        <v>7410609</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1066,11 +1062,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1097,7 +1088,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118793366</v>
+        <v>118793362</v>
       </c>
       <c r="B6" t="n">
         <v>78491</v>
@@ -1137,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>879121</v>
+        <v>879153</v>
       </c>
       <c r="R6" t="n">
-        <v>7410856</v>
+        <v>7410579</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1199,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118793579</v>
+        <v>118794496</v>
       </c>
       <c r="B7" t="n">
         <v>57290</v>
@@ -1233,16 +1224,20 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Turkinrova, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>879307</v>
+        <v>879055</v>
       </c>
       <c r="R7" t="n">
-        <v>7410761</v>
+        <v>7410850</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1279,7 +1274,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Avbarkat</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1299,14 +1294,14 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson, Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118793377</v>
+        <v>118793368</v>
       </c>
       <c r="B8" t="n">
         <v>78491</v>
@@ -1346,10 +1341,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>879103</v>
+        <v>879068</v>
       </c>
       <c r="R8" t="n">
-        <v>7410568</v>
+        <v>7410854</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1408,10 +1403,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118793372</v>
+        <v>118793577</v>
       </c>
       <c r="B9" t="n">
-        <v>78491</v>
+        <v>57290</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1424,21 +1419,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1448,10 +1443,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>879147</v>
+        <v>879114</v>
       </c>
       <c r="R9" t="n">
-        <v>7410683</v>
+        <v>7410564</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1484,6 +1479,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1510,10 +1510,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118793365</v>
+        <v>118793579</v>
       </c>
       <c r="B10" t="n">
-        <v>78491</v>
+        <v>57290</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1526,21 +1526,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1550,10 +1550,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>879126</v>
+        <v>879307</v>
       </c>
       <c r="R10" t="n">
-        <v>7410862</v>
+        <v>7410761</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1586,6 +1586,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Avbarkat</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1612,7 +1617,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118793370</v>
+        <v>118793367</v>
       </c>
       <c r="B11" t="n">
         <v>78491</v>
@@ -1652,10 +1657,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>879185</v>
+        <v>879104</v>
       </c>
       <c r="R11" t="n">
-        <v>7410814</v>
+        <v>7410851</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1714,7 +1719,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118793587</v>
+        <v>118793589</v>
       </c>
       <c r="B12" t="n">
         <v>79476</v>
@@ -1754,10 +1759,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>879116</v>
+        <v>879066</v>
       </c>
       <c r="R12" t="n">
-        <v>7410673</v>
+        <v>7410571</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1816,10 +1821,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118793580</v>
+        <v>118793364</v>
       </c>
       <c r="B13" t="n">
-        <v>57290</v>
+        <v>78491</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1832,21 +1837,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1892,11 +1897,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Avbarkat</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1923,10 +1923,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118793585</v>
+        <v>118793587</v>
       </c>
       <c r="B14" t="n">
-        <v>57306</v>
+        <v>79476</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1935,25 +1935,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1963,10 +1963,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>879078</v>
+        <v>879116</v>
       </c>
       <c r="R14" t="n">
-        <v>7410852</v>
+        <v>7410673</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2025,10 +2025,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118793363</v>
+        <v>118793580</v>
       </c>
       <c r="B15" t="n">
-        <v>78491</v>
+        <v>57290</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2041,21 +2041,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2065,10 +2065,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>879291</v>
+        <v>879242</v>
       </c>
       <c r="R15" t="n">
-        <v>7410669</v>
+        <v>7410815</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2101,6 +2101,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Avbarkat</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2127,10 +2132,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118793584</v>
+        <v>118793360</v>
       </c>
       <c r="B16" t="n">
-        <v>57306</v>
+        <v>90529</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2143,21 +2148,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2167,10 +2172,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>879242</v>
+        <v>879042</v>
       </c>
       <c r="R16" t="n">
-        <v>7410814</v>
+        <v>7410510</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2203,6 +2208,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2229,10 +2239,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118793577</v>
+        <v>118793365</v>
       </c>
       <c r="B17" t="n">
-        <v>57290</v>
+        <v>78491</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2245,21 +2255,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2269,10 +2279,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>879114</v>
+        <v>879126</v>
       </c>
       <c r="R17" t="n">
-        <v>7410564</v>
+        <v>7410862</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2305,11 +2315,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Bohål</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2336,10 +2341,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118793586</v>
+        <v>118793372</v>
       </c>
       <c r="B18" t="n">
-        <v>57306</v>
+        <v>78491</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2352,21 +2357,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2376,10 +2381,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>879119</v>
+        <v>879147</v>
       </c>
       <c r="R18" t="n">
-        <v>7410609</v>
+        <v>7410683</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2438,10 +2443,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118793359</v>
+        <v>118793366</v>
       </c>
       <c r="B19" t="n">
-        <v>90565</v>
+        <v>78491</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2454,21 +2459,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3277</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(O.F.Müll.:Fr.) Dentinger &amp; D.J.McLaughlin</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2478,10 +2483,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>879308</v>
+        <v>879121</v>
       </c>
       <c r="R19" t="n">
-        <v>7410737</v>
+        <v>7410856</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2540,10 +2545,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118793373</v>
+        <v>118793359</v>
       </c>
       <c r="B20" t="n">
-        <v>78491</v>
+        <v>90565</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2556,21 +2561,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>3277</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(O.F.Müll.:Fr.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2580,10 +2585,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>879116</v>
+        <v>879308</v>
       </c>
       <c r="R20" t="n">
-        <v>7410673</v>
+        <v>7410737</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2642,10 +2647,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118793589</v>
+        <v>118793586</v>
       </c>
       <c r="B21" t="n">
-        <v>79476</v>
+        <v>57306</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2654,25 +2659,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2682,10 +2687,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>879066</v>
+        <v>879119</v>
       </c>
       <c r="R21" t="n">
-        <v>7410571</v>
+        <v>7410609</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2744,7 +2749,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118793374</v>
+        <v>118793371</v>
       </c>
       <c r="B22" t="n">
         <v>78491</v>
@@ -2784,10 +2789,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>879113</v>
+        <v>879153</v>
       </c>
       <c r="R22" t="n">
-        <v>7410609</v>
+        <v>7410722</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2846,10 +2851,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118793368</v>
+        <v>118793588</v>
       </c>
       <c r="B23" t="n">
-        <v>78491</v>
+        <v>79476</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2858,25 +2863,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2886,10 +2891,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>879068</v>
+        <v>879064</v>
       </c>
       <c r="R23" t="n">
-        <v>7410854</v>
+        <v>7410567</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2948,10 +2953,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118793371</v>
+        <v>118793584</v>
       </c>
       <c r="B24" t="n">
-        <v>78491</v>
+        <v>57306</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2964,21 +2969,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2988,10 +2993,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>879153</v>
+        <v>879242</v>
       </c>
       <c r="R24" t="n">
-        <v>7410722</v>
+        <v>7410814</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3050,10 +3055,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118793588</v>
+        <v>118793373</v>
       </c>
       <c r="B25" t="n">
-        <v>79476</v>
+        <v>78491</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3062,25 +3067,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3090,10 +3095,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>879064</v>
+        <v>879116</v>
       </c>
       <c r="R25" t="n">
-        <v>7410567</v>
+        <v>7410673</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3152,7 +3157,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118793364</v>
+        <v>118793377</v>
       </c>
       <c r="B26" t="n">
         <v>78491</v>
@@ -3192,10 +3197,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>879242</v>
+        <v>879103</v>
       </c>
       <c r="R26" t="n">
-        <v>7410815</v>
+        <v>7410568</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3254,10 +3259,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118793578</v>
+        <v>118793370</v>
       </c>
       <c r="B27" t="n">
-        <v>57290</v>
+        <v>78491</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3270,21 +3275,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3294,10 +3299,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>879261</v>
+        <v>879185</v>
       </c>
       <c r="R27" t="n">
-        <v>7410686</v>
+        <v>7410814</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3330,11 +3335,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Avbarkat</t>
         </is>
       </c>
       <c r="AD27" t="b">
